--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/21.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/21.xlsx
@@ -426,13 +426,13 @@
         <v>-20.87702702451955</v>
       </c>
       <c r="E2">
-        <v>-53.67471840300617</v>
+        <v>-36.40425971320136</v>
       </c>
       <c r="F2">
-        <v>-9.745268084111041</v>
+        <v>-5.525324114051654</v>
       </c>
       <c r="G2">
-        <v>-33.24186757232587</v>
+        <v>-20.72017599368041</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-20.38576851013127</v>
       </c>
       <c r="E3">
-        <v>-53.28037322582573</v>
+        <v>-36.4673390918912</v>
       </c>
       <c r="F3">
-        <v>-9.639890470093334</v>
+        <v>-5.422901893235396</v>
       </c>
       <c r="G3">
-        <v>-33.51345976254937</v>
+        <v>-21.31973565411566</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.816592178807</v>
       </c>
       <c r="E4">
-        <v>-53.81786459850714</v>
+        <v>-36.86585386151421</v>
       </c>
       <c r="F4">
-        <v>-9.559270732688454</v>
+        <v>-5.620071696001692</v>
       </c>
       <c r="G4">
-        <v>-33.34256609126665</v>
+        <v>-21.33084418967268</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.20206414969072</v>
       </c>
       <c r="E5">
-        <v>-53.67447612964676</v>
+        <v>-37.14095186476917</v>
       </c>
       <c r="F5">
-        <v>-9.603676064888221</v>
+        <v>-5.296451686270091</v>
       </c>
       <c r="G5">
-        <v>-33.55060242822723</v>
+        <v>-21.2520929323845</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.56447377299188</v>
       </c>
       <c r="E6">
-        <v>-53.61137750494238</v>
+        <v>-37.49391471434902</v>
       </c>
       <c r="F6">
-        <v>-9.574082144299361</v>
+        <v>-5.549573819028862</v>
       </c>
       <c r="G6">
-        <v>-33.14520129785193</v>
+        <v>-21.15836973289496</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.92731510773912</v>
       </c>
       <c r="E7">
-        <v>-54.177032589596</v>
+        <v>-36.98538293294667</v>
       </c>
       <c r="F7">
-        <v>-9.523484324006986</v>
+        <v>-5.531479978944967</v>
       </c>
       <c r="G7">
-        <v>-33.31723710734569</v>
+        <v>-20.60921478356789</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.32742037094612</v>
       </c>
       <c r="E8">
-        <v>-54.32108447989849</v>
+        <v>-38.80599250909443</v>
       </c>
       <c r="F8">
-        <v>-9.655549956221961</v>
+        <v>-5.182544430155066</v>
       </c>
       <c r="G8">
-        <v>-33.15229165876066</v>
+        <v>-20.63870346795895</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.79238526893265</v>
       </c>
       <c r="E9">
-        <v>-53.96051719034126</v>
+        <v>-36.90389077894164</v>
       </c>
       <c r="F9">
-        <v>-9.625337598473122</v>
+        <v>-5.316201290888579</v>
       </c>
       <c r="G9">
-        <v>-33.00637688120813</v>
+        <v>-21.37686077266855</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.33969885355621</v>
       </c>
       <c r="E10">
-        <v>-54.42806288561869</v>
+        <v>-38.21007023629205</v>
       </c>
       <c r="F10">
-        <v>-9.580916231250962</v>
+        <v>-5.388166471392062</v>
       </c>
       <c r="G10">
-        <v>-32.97365213855243</v>
+        <v>-19.64377528540516</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.97633087707001</v>
       </c>
       <c r="E11">
-        <v>-54.17337245047929</v>
+        <v>-38.63332858789297</v>
       </c>
       <c r="F11">
-        <v>-9.622929573628696</v>
+        <v>-5.188627444576269</v>
       </c>
       <c r="G11">
-        <v>-32.91915228261218</v>
+        <v>-20.05775072872717</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.71194034982801</v>
       </c>
       <c r="E12">
-        <v>-54.44654472016249</v>
+        <v>-38.49601619903239</v>
       </c>
       <c r="F12">
-        <v>-9.590521011701622</v>
+        <v>-5.29384411448032</v>
       </c>
       <c r="G12">
-        <v>-32.54273084025127</v>
+        <v>-19.91744318768178</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.53694909340881</v>
       </c>
       <c r="E13">
-        <v>-54.63394542790341</v>
+        <v>-39.92966087851371</v>
       </c>
       <c r="F13">
-        <v>-9.591360375836805</v>
+        <v>-5.310313072294975</v>
       </c>
       <c r="G13">
-        <v>-32.71160921693696</v>
+        <v>-19.71313452499843</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.45277203297659</v>
       </c>
       <c r="E14">
-        <v>-54.69812182942162</v>
+        <v>-40.21168744700041</v>
       </c>
       <c r="F14">
-        <v>-9.565671280145702</v>
+        <v>-5.224441370148017</v>
       </c>
       <c r="G14">
-        <v>-32.40022757987696</v>
+        <v>-20.072130083277</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.44201696704293</v>
       </c>
       <c r="E15">
-        <v>-55.15338403895324</v>
+        <v>-40.73660098312551</v>
       </c>
       <c r="F15">
-        <v>-9.615865453392878</v>
+        <v>-5.542413092732203</v>
       </c>
       <c r="G15">
-        <v>-32.45137302554954</v>
+        <v>-18.85581578887553</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.48047857397626</v>
       </c>
       <c r="E16">
-        <v>-55.01365231285406</v>
+        <v>-41.49958771901886</v>
       </c>
       <c r="F16">
-        <v>-9.572122308229005</v>
+        <v>-5.084147197922898</v>
       </c>
       <c r="G16">
-        <v>-32.53051906539329</v>
+        <v>-18.83698871639369</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-15.53810357371489</v>
       </c>
       <c r="E17">
-        <v>-55.64767037324597</v>
+        <v>-41.49487357757688</v>
       </c>
       <c r="F17">
-        <v>-9.57008170315696</v>
+        <v>-4.971759507633737</v>
       </c>
       <c r="G17">
-        <v>-32.0592099391494</v>
+        <v>-19.02093255819222</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-15.59584105257889</v>
       </c>
       <c r="E18">
-        <v>-55.91996072261617</v>
+        <v>-41.48028509856116</v>
       </c>
       <c r="F18">
-        <v>-9.483957003990012</v>
+        <v>-4.768768793775244</v>
       </c>
       <c r="G18">
-        <v>-31.94367189982884</v>
+        <v>-18.09675238908542</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-15.62956992008576</v>
       </c>
       <c r="E19">
-        <v>-56.19144500361302</v>
+        <v>-40.88873280317619</v>
       </c>
       <c r="F19">
-        <v>-9.491349743203283</v>
+        <v>-5.077443370782843</v>
       </c>
       <c r="G19">
-        <v>-32.0304379878676</v>
+        <v>-17.82582230796978</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-15.6339444829275</v>
       </c>
       <c r="E20">
-        <v>-56.01214007527931</v>
+        <v>-42.43926645374349</v>
       </c>
       <c r="F20">
-        <v>-9.294029488375021</v>
+        <v>-4.698418993305508</v>
       </c>
       <c r="G20">
-        <v>-31.56742922692705</v>
+        <v>-17.48555450580687</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-15.59889221848452</v>
       </c>
       <c r="E21">
-        <v>-55.81229625308382</v>
+        <v>-43.30728208729674</v>
       </c>
       <c r="F21">
-        <v>-9.269101957266004</v>
+        <v>-4.508384577541225</v>
       </c>
       <c r="G21">
-        <v>-31.71837437842651</v>
+        <v>-17.26837278679406</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-15.51634920981098</v>
       </c>
       <c r="E22">
-        <v>-56.06496812093429</v>
+        <v>-42.60624261159132</v>
       </c>
       <c r="F22">
-        <v>-9.349133347923299</v>
+        <v>-3.983033692006863</v>
       </c>
       <c r="G22">
-        <v>-31.78759457510713</v>
+        <v>-17.05564044098603</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-15.37974094742156</v>
       </c>
       <c r="E23">
-        <v>-56.54724381004017</v>
+        <v>-42.38201974957553</v>
       </c>
       <c r="F23">
-        <v>-9.274938705417355</v>
+        <v>-4.513640105621611</v>
       </c>
       <c r="G23">
-        <v>-31.71745570203936</v>
+        <v>-17.58543366472668</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-15.1927339381235</v>
       </c>
       <c r="E24">
-        <v>-56.75744991288372</v>
+        <v>-44.25988735107627</v>
       </c>
       <c r="F24">
-        <v>-9.32461639257286</v>
+        <v>-4.095327151794055</v>
       </c>
       <c r="G24">
-        <v>-31.68962560096348</v>
+        <v>-17.02428957472913</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-14.95493693013165</v>
       </c>
       <c r="E25">
-        <v>-56.46670263557675</v>
+        <v>-43.62492510385377</v>
       </c>
       <c r="F25">
-        <v>-9.076596168420677</v>
+        <v>-4.005371863944137</v>
       </c>
       <c r="G25">
-        <v>-31.43944188110606</v>
+        <v>-17.33112583276372</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-14.67878054721781</v>
       </c>
       <c r="E26">
-        <v>-56.5698125923759</v>
+        <v>-44.46444984318776</v>
       </c>
       <c r="F26">
-        <v>-8.953662580440605</v>
+        <v>-4.556796883670294</v>
       </c>
       <c r="G26">
-        <v>-31.64345507760003</v>
+        <v>-17.55234972787997</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-14.36968216537046</v>
       </c>
       <c r="E27">
-        <v>-56.61877218910983</v>
+        <v>-43.589046004291</v>
       </c>
       <c r="F27">
-        <v>-9.014915178205579</v>
+        <v>-4.283427070782629</v>
       </c>
       <c r="G27">
-        <v>-31.70084835034161</v>
+        <v>-17.5251734595481</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-14.03121127698312</v>
       </c>
       <c r="E28">
-        <v>-56.45689282875763</v>
+        <v>-44.25135344180882</v>
       </c>
       <c r="F28">
-        <v>-9.023881725172318</v>
+        <v>-3.946382777858806</v>
       </c>
       <c r="G28">
-        <v>-31.58048022507925</v>
+        <v>-17.09715633732126</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-13.66633320012812</v>
       </c>
       <c r="E29">
-        <v>-56.52044090450728</v>
+        <v>-43.29901535799574</v>
       </c>
       <c r="F29">
-        <v>-9.038072917954091</v>
+        <v>-3.95422924881685</v>
       </c>
       <c r="G29">
-        <v>-31.89845646885347</v>
+        <v>-17.04982381247353</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-13.28292097680321</v>
       </c>
       <c r="E30">
-        <v>-56.26441117318011</v>
+        <v>-43.77678295122698</v>
       </c>
       <c r="F30">
-        <v>-9.034402679495061</v>
+        <v>-3.934184283045133</v>
       </c>
       <c r="G30">
-        <v>-31.55954599036167</v>
+        <v>-17.63867882390755</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-12.88526703693434</v>
       </c>
       <c r="E31">
-        <v>-56.2454583773395</v>
+        <v>-44.65783379721132</v>
       </c>
       <c r="F31">
-        <v>-8.987735221358328</v>
+        <v>-4.051404651935258</v>
       </c>
       <c r="G31">
-        <v>-31.99373231420093</v>
+        <v>-17.47555003718719</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-12.48755335109124</v>
       </c>
       <c r="E32">
-        <v>-56.73495018977661</v>
+        <v>-43.21003990069303</v>
       </c>
       <c r="F32">
-        <v>-9.066062148524132</v>
+        <v>-4.232777780048003</v>
       </c>
       <c r="G32">
-        <v>-31.67409417656599</v>
+        <v>-17.68734715388037</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-12.0964542087819</v>
       </c>
       <c r="E33">
-        <v>-56.73587852694818</v>
+        <v>-42.65764758428939</v>
       </c>
       <c r="F33">
-        <v>-9.071870785895484</v>
+        <v>-4.060647951510719</v>
       </c>
       <c r="G33">
-        <v>-31.83389255447384</v>
+        <v>-18.25040639447239</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.71590599982972</v>
       </c>
       <c r="E34">
-        <v>-56.10353260558361</v>
+        <v>-41.80920401539729</v>
       </c>
       <c r="F34">
-        <v>-8.92845314967864</v>
+        <v>-3.901364353506524</v>
       </c>
       <c r="G34">
-        <v>-32.21703026609754</v>
+        <v>-18.63893036368848</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.34924277205487</v>
       </c>
       <c r="E35">
-        <v>-55.76141884760764</v>
+        <v>-41.95289023142367</v>
       </c>
       <c r="F35">
-        <v>-9.07965074120508</v>
+        <v>-3.752832534962247</v>
       </c>
       <c r="G35">
-        <v>-31.9981552030414</v>
+        <v>-17.84263656876374</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.00251118517582</v>
       </c>
       <c r="E36">
-        <v>-56.16432170854407</v>
+        <v>-42.49893815574256</v>
       </c>
       <c r="F36">
-        <v>-9.067920231489421</v>
+        <v>-4.075481732967683</v>
       </c>
       <c r="G36">
-        <v>-31.82573702553784</v>
+        <v>-18.76026516824831</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.6791620743681</v>
       </c>
       <c r="E37">
-        <v>-56.0903015366517</v>
+        <v>-42.52195638912355</v>
       </c>
       <c r="F37">
-        <v>-9.060198477372218</v>
+        <v>-3.570597078978545</v>
       </c>
       <c r="G37">
-        <v>-31.77564102280121</v>
+        <v>-18.37268304923814</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.38956860494078</v>
       </c>
       <c r="E38">
-        <v>-55.55891001845863</v>
+        <v>-41.67790091154489</v>
       </c>
       <c r="F38">
-        <v>-9.100541405935642</v>
+        <v>-3.548982660644628</v>
       </c>
       <c r="G38">
-        <v>-31.76156210025907</v>
+        <v>-18.09999672371391</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.13650896522834</v>
       </c>
       <c r="E39">
-        <v>-55.87561337665906</v>
+        <v>-41.92746058563359</v>
       </c>
       <c r="F39">
-        <v>-9.167743986824922</v>
+        <v>-3.991106632910816</v>
       </c>
       <c r="G39">
-        <v>-31.92409167823682</v>
+        <v>-18.94422887332007</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.918819623455732</v>
       </c>
       <c r="E40">
-        <v>-55.86527487049955</v>
+        <v>-40.06196703935881</v>
       </c>
       <c r="F40">
-        <v>-9.064483193726439</v>
+        <v>-3.872851312204952</v>
       </c>
       <c r="G40">
-        <v>-32.30074485878548</v>
+        <v>-18.71058712188601</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.734694352432376</v>
       </c>
       <c r="E41">
-        <v>-55.61056632146412</v>
+        <v>-40.04504639622915</v>
       </c>
       <c r="F41">
-        <v>-9.023080369979105</v>
+        <v>-3.861768538208707</v>
       </c>
       <c r="G41">
-        <v>-32.0360311545562</v>
+        <v>-18.24459969759651</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.583444982373168</v>
       </c>
       <c r="E42">
-        <v>-55.12824647973667</v>
+        <v>-40.07515848414315</v>
       </c>
       <c r="F42">
-        <v>-9.029188723694954</v>
+        <v>-3.585679502264233</v>
       </c>
       <c r="G42">
-        <v>-32.07304636423079</v>
+        <v>-19.24902086948415</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.462835342158378</v>
       </c>
       <c r="E43">
-        <v>-55.21350292776057</v>
+        <v>-39.0568269486163</v>
       </c>
       <c r="F43">
-        <v>-9.046002929399176</v>
+        <v>-3.883017120476158</v>
       </c>
       <c r="G43">
-        <v>-31.99249251489647</v>
+        <v>-18.88206841500195</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.374979525242351</v>
       </c>
       <c r="E44">
-        <v>-54.63536397238632</v>
+        <v>-40.26399585026301</v>
       </c>
       <c r="F44">
-        <v>-9.083233875838763</v>
+        <v>-3.917945754441175</v>
       </c>
       <c r="G44">
-        <v>-32.20492277342404</v>
+        <v>-19.5234998554179</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.315941780238237</v>
       </c>
       <c r="E45">
-        <v>-55.05182168814622</v>
+        <v>-38.91894397203075</v>
       </c>
       <c r="F45">
-        <v>-9.011534362002594</v>
+        <v>-4.00604097969341</v>
       </c>
       <c r="G45">
-        <v>-31.91288630922277</v>
+        <v>-19.44720998873816</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.27802022879338</v>
       </c>
       <c r="E46">
-        <v>-54.85619387525186</v>
+        <v>-38.13817165447227</v>
       </c>
       <c r="F46">
-        <v>-9.05380070140032</v>
+        <v>-3.835014202326231</v>
       </c>
       <c r="G46">
-        <v>-32.07935957457418</v>
+        <v>-19.38956180399006</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.254762715236271</v>
       </c>
       <c r="E47">
-        <v>-54.2916935514702</v>
+        <v>-38.01042566695289</v>
       </c>
       <c r="F47">
-        <v>-9.097592941447573</v>
+        <v>-3.912692601919662</v>
       </c>
       <c r="G47">
-        <v>-31.98593184127402</v>
+        <v>-19.36781483034259</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.241452647873558</v>
       </c>
       <c r="E48">
-        <v>-54.12654350076598</v>
+        <v>-37.94090453398714</v>
       </c>
       <c r="F48">
-        <v>-9.189338212908417</v>
+        <v>-3.721691333694003</v>
       </c>
       <c r="G48">
-        <v>-31.68126647347682</v>
+        <v>-19.06807803721698</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.234455706498995</v>
       </c>
       <c r="E49">
-        <v>-54.1290398220627</v>
+        <v>-38.38684827612948</v>
       </c>
       <c r="F49">
-        <v>-9.133671741833679</v>
+        <v>-3.572693905610587</v>
       </c>
       <c r="G49">
-        <v>-32.23419213417312</v>
+        <v>-18.98571166419991</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.234677866994478</v>
       </c>
       <c r="E50">
-        <v>-54.3818396193039</v>
+        <v>-36.04631101373906</v>
       </c>
       <c r="F50">
-        <v>-9.133861390617053</v>
+        <v>-4.083840532789373</v>
       </c>
       <c r="G50">
-        <v>-32.40815799171629</v>
+        <v>-19.27061721330959</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.239919317937444</v>
       </c>
       <c r="E51">
-        <v>-53.88102435761061</v>
+        <v>-36.86006647173241</v>
       </c>
       <c r="F51">
-        <v>-9.214220212472366</v>
+        <v>-3.607032609122103</v>
       </c>
       <c r="G51">
-        <v>-32.13735619424028</v>
+        <v>-19.41379168679199</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.245575615397851</v>
       </c>
       <c r="E52">
-        <v>-53.97291954852977</v>
+        <v>-36.96201374283009</v>
       </c>
       <c r="F52">
-        <v>-9.04246651409</v>
+        <v>-3.592867151561455</v>
       </c>
       <c r="G52">
-        <v>-31.96067651699131</v>
+        <v>-19.51589718758696</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.249944003708551</v>
       </c>
       <c r="E53">
-        <v>-53.81805366229695</v>
+        <v>-35.88250931617062</v>
       </c>
       <c r="F53">
-        <v>-9.234486105219286</v>
+        <v>-3.539568320830297</v>
       </c>
       <c r="G53">
-        <v>-32.32445084775581</v>
+        <v>-19.58178532018231</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.25274549448133</v>
       </c>
       <c r="E54">
-        <v>-53.4445451261443</v>
+        <v>-35.28892147171919</v>
       </c>
       <c r="F54">
-        <v>-9.245161470868785</v>
+        <v>-3.964877295539308</v>
       </c>
       <c r="G54">
-        <v>-32.20163043588524</v>
+        <v>-19.1765861330849</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.254861662647638</v>
       </c>
       <c r="E55">
-        <v>-53.1440955932759</v>
+        <v>-34.41348366926737</v>
       </c>
       <c r="F55">
-        <v>-9.220005490181466</v>
+        <v>-4.201590651308211</v>
       </c>
       <c r="G55">
-        <v>-32.12965503767956</v>
+        <v>-19.34186015331471</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.259491689251188</v>
       </c>
       <c r="E56">
-        <v>-53.41336205412748</v>
+        <v>-34.94017689567749</v>
       </c>
       <c r="F56">
-        <v>-9.205502703260828</v>
+        <v>-3.805575484917084</v>
       </c>
       <c r="G56">
-        <v>-31.95763247036795</v>
+        <v>-19.60498562332152</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.266709005555747</v>
       </c>
       <c r="E57">
-        <v>-53.08487560655909</v>
+        <v>-34.87374871045897</v>
       </c>
       <c r="F57">
-        <v>-9.394660537800917</v>
+        <v>-3.813315847578795</v>
       </c>
       <c r="G57">
-        <v>-32.11193782558976</v>
+        <v>-20.0173819364213</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.272997951355572</v>
       </c>
       <c r="E58">
-        <v>-53.1129815804877</v>
+        <v>-34.39876160026844</v>
       </c>
       <c r="F58">
-        <v>-9.293489444657856</v>
+        <v>-3.931103183186646</v>
       </c>
       <c r="G58">
-        <v>-32.26169200833147</v>
+        <v>-19.77289318252781</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.278136060733996</v>
       </c>
       <c r="E59">
-        <v>-52.99969614259332</v>
+        <v>-34.43362179317948</v>
       </c>
       <c r="F59">
-        <v>-9.234625867266324</v>
+        <v>-4.20034427475276</v>
       </c>
       <c r="G59">
-        <v>-32.52176763826022</v>
+        <v>-19.03254926248952</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.281853709962355</v>
       </c>
       <c r="E60">
-        <v>-52.91795605463636</v>
+        <v>-33.7416392654894</v>
       </c>
       <c r="F60">
-        <v>-9.20041504800748</v>
+        <v>-4.357303784326048</v>
       </c>
       <c r="G60">
-        <v>-32.45706385333155</v>
+        <v>-20.07972944056239</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.285735283091839</v>
       </c>
       <c r="E61">
-        <v>-52.17309340384021</v>
+        <v>-33.61166300452124</v>
       </c>
       <c r="F61">
-        <v>-9.463983107021249</v>
+        <v>-4.148371797725784</v>
       </c>
       <c r="G61">
-        <v>-32.43206509632813</v>
+        <v>-19.71100915476222</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.292839846834569</v>
       </c>
       <c r="E62">
-        <v>-52.72229767454245</v>
+        <v>-32.5863757329186</v>
       </c>
       <c r="F62">
-        <v>-9.585682592166716</v>
+        <v>-4.480128888450913</v>
       </c>
       <c r="G62">
-        <v>-32.43176549195682</v>
+        <v>-20.0720423538202</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.303351707057098</v>
       </c>
       <c r="E63">
-        <v>-52.45602453500994</v>
+        <v>-32.8286106002999</v>
       </c>
       <c r="F63">
-        <v>-9.370647596858065</v>
+        <v>-4.481056148264402</v>
       </c>
       <c r="G63">
-        <v>-32.4275859282135</v>
+        <v>-20.05995058623802</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.313411653582778</v>
       </c>
       <c r="E64">
-        <v>-52.21140995453761</v>
+        <v>-33.38645746364579</v>
       </c>
       <c r="F64">
-        <v>-9.258089658182996</v>
+        <v>-4.639804453669179</v>
       </c>
       <c r="G64">
-        <v>-32.65809424829464</v>
+        <v>-19.95621629703772</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.323151281179404</v>
       </c>
       <c r="E65">
-        <v>-52.46659286122534</v>
+        <v>-33.03205908780551</v>
       </c>
       <c r="F65">
-        <v>-9.449195648962313</v>
+        <v>-4.346601099749509</v>
       </c>
       <c r="G65">
-        <v>-32.14790110941925</v>
+        <v>-20.35829032914606</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.331381352406584</v>
       </c>
       <c r="E66">
-        <v>-52.65534192210205</v>
+        <v>-32.77994082590246</v>
       </c>
       <c r="F66">
-        <v>-9.232165976053167</v>
+        <v>-4.426961505310737</v>
       </c>
       <c r="G66">
-        <v>-32.47754454331025</v>
+        <v>-19.6267590813333</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.339391362128174</v>
       </c>
       <c r="E67">
-        <v>-52.15799433938013</v>
+        <v>-33.30482719118352</v>
       </c>
       <c r="F67">
-        <v>-9.40788289848892</v>
+        <v>-4.632062507301553</v>
       </c>
       <c r="G67">
-        <v>-32.49979223697054</v>
+        <v>-20.05182154166634</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.348926698880888</v>
       </c>
       <c r="E68">
-        <v>-52.18689958897109</v>
+        <v>-32.1233324729233</v>
       </c>
       <c r="F68">
-        <v>-9.476603659461388</v>
+        <v>-4.863528253519648</v>
       </c>
       <c r="G68">
-        <v>-32.50486895855502</v>
+        <v>-19.28118944048925</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.359079105362857</v>
       </c>
       <c r="E69">
-        <v>-52.6011768444963</v>
+        <v>-33.162825567488</v>
       </c>
       <c r="F69">
-        <v>-9.44032075897543</v>
+        <v>-5.117935563628799</v>
       </c>
       <c r="G69">
-        <v>-32.48282651871816</v>
+        <v>-20.04934690887573</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.364701614961666</v>
       </c>
       <c r="E70">
-        <v>-52.49172815620491</v>
+        <v>-32.5543141369443</v>
       </c>
       <c r="F70">
-        <v>-9.562792102791432</v>
+        <v>-4.913882183101046</v>
       </c>
       <c r="G70">
-        <v>-32.26166883451269</v>
+        <v>-19.75367712094511</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.365597713821236</v>
       </c>
       <c r="E71">
-        <v>-52.58833409221054</v>
+        <v>-33.07195720805009</v>
       </c>
       <c r="F71">
-        <v>-9.599853394734827</v>
+        <v>-4.950834001373036</v>
       </c>
       <c r="G71">
-        <v>-32.45621718130988</v>
+        <v>-19.54197932061811</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.359557077552378</v>
       </c>
       <c r="E72">
-        <v>-51.57235736316768</v>
+        <v>-31.5046659394174</v>
       </c>
       <c r="F72">
-        <v>-9.597363017182801</v>
+        <v>-5.138084262137977</v>
       </c>
       <c r="G72">
-        <v>-32.37728218874427</v>
+        <v>-19.54196111261764</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.348187208134204</v>
       </c>
       <c r="E73">
-        <v>-52.26418705486</v>
+        <v>-33.32156443111587</v>
       </c>
       <c r="F73">
-        <v>-9.550672595310292</v>
+        <v>-4.947591363511174</v>
       </c>
       <c r="G73">
-        <v>-32.52251830446125</v>
+        <v>-19.55687346499929</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.333118214831201</v>
       </c>
       <c r="E74">
-        <v>-52.61448942596035</v>
+        <v>-33.52147844465848</v>
       </c>
       <c r="F74">
-        <v>-9.502491906171358</v>
+        <v>-5.405395608046129</v>
       </c>
       <c r="G74">
-        <v>-32.2961481663042</v>
+        <v>-18.87143825327535</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.313729697857656</v>
       </c>
       <c r="E75">
-        <v>-52.66892281565105</v>
+        <v>-33.15899447847751</v>
       </c>
       <c r="F75">
-        <v>-9.638886004616467</v>
+        <v>-5.100531427471077</v>
       </c>
       <c r="G75">
-        <v>-32.36186083998596</v>
+        <v>-19.32939594935935</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.285631335437081</v>
       </c>
       <c r="E76">
-        <v>-52.57503962464253</v>
+        <v>-33.8591259951444</v>
       </c>
       <c r="F76">
-        <v>-9.602610626733608</v>
+        <v>-5.144876776809297</v>
       </c>
       <c r="G76">
-        <v>-32.06456474655918</v>
+        <v>-18.78130699569592</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.250327149607358</v>
       </c>
       <c r="E77">
-        <v>-53.16345595177719</v>
+        <v>-32.97353308973037</v>
       </c>
       <c r="F77">
-        <v>-9.518885637955028</v>
+        <v>-4.916714641130809</v>
       </c>
       <c r="G77">
-        <v>-32.13868620591069</v>
+        <v>-19.12346015354344</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.206756277061606</v>
       </c>
       <c r="E78">
-        <v>-52.67917867715992</v>
+        <v>-33.12223232648324</v>
       </c>
       <c r="F78">
-        <v>-9.716419297155397</v>
+        <v>-5.560449127550185</v>
       </c>
       <c r="G78">
-        <v>-31.97604572465737</v>
+        <v>-18.74866501667871</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.158600111356268</v>
       </c>
       <c r="E79">
-        <v>-53.19661796693536</v>
+        <v>-34.27951782269846</v>
       </c>
       <c r="F79">
-        <v>-9.81127298740177</v>
+        <v>-5.812332010430125</v>
       </c>
       <c r="G79">
-        <v>-32.29936270602283</v>
+        <v>-18.99628554665234</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.10865771883496</v>
       </c>
       <c r="E80">
-        <v>-53.15414201286192</v>
+        <v>-34.38362291166079</v>
       </c>
       <c r="F80">
-        <v>-9.721435289716073</v>
+        <v>-5.24156360665279</v>
       </c>
       <c r="G80">
-        <v>-31.67490194967757</v>
+        <v>-19.10423416032413</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.05744243877391</v>
       </c>
       <c r="E81">
-        <v>-53.36144762810355</v>
+        <v>-35.5045379688834</v>
       </c>
       <c r="F81">
-        <v>-9.778226587917253</v>
+        <v>-5.366807821563488</v>
       </c>
       <c r="G81">
-        <v>-31.83824261131244</v>
+        <v>-18.45038651886314</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.000950496262373</v>
       </c>
       <c r="E82">
-        <v>-53.3526193680256</v>
+        <v>-35.24171439442623</v>
       </c>
       <c r="F82">
-        <v>-9.701723298113077</v>
+        <v>-5.846139380607011</v>
       </c>
       <c r="G82">
-        <v>-32.11445135729046</v>
+        <v>-17.93001510772726</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.940700369480853</v>
       </c>
       <c r="E83">
-        <v>-53.71392593096458</v>
+        <v>-35.06308420871967</v>
       </c>
       <c r="F83">
-        <v>-9.738477549072117</v>
+        <v>-5.693602369802588</v>
       </c>
       <c r="G83">
-        <v>-32.09177991380114</v>
+        <v>-18.21994606496555</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.873667484296901</v>
       </c>
       <c r="E84">
-        <v>-53.7668343570332</v>
+        <v>-37.34117155030731</v>
       </c>
       <c r="F84">
-        <v>-9.689653875331512</v>
+        <v>-5.70014386708631</v>
       </c>
       <c r="G84">
-        <v>-31.87579247409163</v>
+        <v>-18.13811434505308</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.801691333757049</v>
       </c>
       <c r="E85">
-        <v>-54.36919838411148</v>
+        <v>-36.59387824108754</v>
       </c>
       <c r="F85">
-        <v>-9.627103628532076</v>
+        <v>-5.202571975161714</v>
       </c>
       <c r="G85">
-        <v>-31.85598382485739</v>
+        <v>-18.05237121558595</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.724182859245017</v>
       </c>
       <c r="E86">
-        <v>-54.70258916903018</v>
+        <v>-37.94510922210326</v>
       </c>
       <c r="F86">
-        <v>-9.722777480479408</v>
+        <v>-5.88873156749684</v>
       </c>
       <c r="G86">
-        <v>-31.90935064658683</v>
+        <v>-18.2879711547065</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.638344059223062</v>
       </c>
       <c r="E87">
-        <v>-54.91485685966573</v>
+        <v>-37.56067800664411</v>
       </c>
       <c r="F87">
-        <v>-9.616304337894695</v>
+        <v>-5.580350767936554</v>
       </c>
       <c r="G87">
-        <v>-31.55996311909961</v>
+        <v>-18.59237416176971</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.537435136306694</v>
       </c>
       <c r="E88">
-        <v>-55.3783563634173</v>
+        <v>-38.70012131526911</v>
       </c>
       <c r="F88">
-        <v>-9.780908197958571</v>
+        <v>-5.370348196137454</v>
       </c>
       <c r="G88">
-        <v>-31.64850614245658</v>
+        <v>-17.96999987675058</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.420206448298931</v>
       </c>
       <c r="E89">
-        <v>-55.48292109249142</v>
+        <v>-39.99690871752761</v>
       </c>
       <c r="F89">
-        <v>-9.742620919673385</v>
+        <v>-5.450969913174729</v>
       </c>
       <c r="G89">
-        <v>-31.44684343329549</v>
+        <v>-17.60801820639559</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.280924161102833</v>
       </c>
       <c r="E90">
-        <v>-56.01180949667675</v>
+        <v>-40.938804140279</v>
       </c>
       <c r="F90">
-        <v>-9.723610113864449</v>
+        <v>-5.640584646871421</v>
       </c>
       <c r="G90">
-        <v>-31.79870973175523</v>
+        <v>-18.14719351619453</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.120051148977922</v>
       </c>
       <c r="E91">
-        <v>-56.20251712256177</v>
+        <v>-41.10786339617035</v>
       </c>
       <c r="F91">
-        <v>-9.675204538485522</v>
+        <v>-6.023443968222992</v>
       </c>
       <c r="G91">
-        <v>-31.72801634230964</v>
+        <v>-17.93984080688782</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.935751986251807</v>
       </c>
       <c r="E92">
-        <v>-56.86736390187939</v>
+        <v>-43.01966285341057</v>
       </c>
       <c r="F92">
-        <v>-9.861800728707387</v>
+        <v>-5.719452409607348</v>
       </c>
       <c r="G92">
-        <v>-32.1169185413536</v>
+        <v>-17.36260912084218</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.725296339531248</v>
       </c>
       <c r="E93">
-        <v>-57.29868633356947</v>
+        <v>-43.96397874551906</v>
       </c>
       <c r="F93">
-        <v>-9.737141297205964</v>
+        <v>-5.954582059460812</v>
       </c>
       <c r="G93">
-        <v>-31.80278997913238</v>
+        <v>-18.56810620769409</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.484279005473446</v>
       </c>
       <c r="E94">
-        <v>-57.54709577526022</v>
+        <v>-45.08132762946063</v>
       </c>
       <c r="F94">
-        <v>-9.847472149437447</v>
+        <v>-5.672886704575681</v>
       </c>
       <c r="G94">
-        <v>-31.76102330897255</v>
+        <v>-18.06094552853267</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.21418167053529</v>
       </c>
       <c r="E95">
-        <v>-58.55302948107258</v>
+        <v>-45.50151567568435</v>
       </c>
       <c r="F95">
-        <v>-9.679736708889031</v>
+        <v>-6.217606709382347</v>
       </c>
       <c r="G95">
-        <v>-31.71651881765175</v>
+        <v>-18.19510207596609</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.911275978201955</v>
       </c>
       <c r="E96">
-        <v>-58.67591584992248</v>
+        <v>-47.56165662023083</v>
       </c>
       <c r="F96">
-        <v>-9.763309265973248</v>
+        <v>-6.146081007270398</v>
       </c>
       <c r="G96">
-        <v>-31.69764291462321</v>
+        <v>-19.53485833716314</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.582931469689753</v>
       </c>
       <c r="E97">
-        <v>-59.41338972931587</v>
+        <v>-48.43940507654506</v>
       </c>
       <c r="F97">
-        <v>-9.624149225146825</v>
+        <v>-6.24397343324202</v>
       </c>
       <c r="G97">
-        <v>-32.08100243279804</v>
+        <v>-17.85459094870605</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.227287341608505</v>
       </c>
       <c r="E98">
-        <v>-59.40954958335736</v>
+        <v>-50.09972139036182</v>
       </c>
       <c r="F98">
-        <v>-9.723876968311201</v>
+        <v>-5.916652302786037</v>
       </c>
       <c r="G98">
-        <v>-31.82164684652408</v>
+        <v>-18.33598730720809</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.852245869077691</v>
       </c>
       <c r="E99">
-        <v>-60.8626304732796</v>
+        <v>-51.92291219669395</v>
       </c>
       <c r="F99">
-        <v>-9.872434918003083</v>
+        <v>-6.348947796141008</v>
       </c>
       <c r="G99">
-        <v>-32.04782000722154</v>
+        <v>-18.81310975141893</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.4475112700396</v>
       </c>
       <c r="E100">
-        <v>-60.68139867925563</v>
+        <v>-52.45277648702794</v>
       </c>
       <c r="F100">
-        <v>-9.803384548236965</v>
+        <v>-6.168845196098925</v>
       </c>
       <c r="G100">
-        <v>-32.13561153674109</v>
+        <v>-18.84058727939488</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.033500369187973</v>
       </c>
       <c r="E101">
-        <v>-61.73475343275781</v>
+        <v>-54.69440055590582</v>
       </c>
       <c r="F101">
-        <v>-9.697927155033769</v>
+        <v>-6.077552864529896</v>
       </c>
       <c r="G101">
-        <v>-32.23541372547712</v>
+        <v>-19.09134124072144</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.585332960550883</v>
       </c>
       <c r="E102">
-        <v>-62.57152938836914</v>
+        <v>-54.8252247736319</v>
       </c>
       <c r="F102">
-        <v>-9.671037808222001</v>
+        <v>-6.334079173153905</v>
       </c>
       <c r="G102">
-        <v>-31.90949548295417</v>
+        <v>-18.8586628580393</v>
       </c>
     </row>
   </sheetData>
